--- a/data.mn/public/datasets/birth-rate-by-age.xlsx
+++ b/data.mn/public/datasets/birth-rate-by-age.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1459,4 +1460,1058 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B2" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D2" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>249.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>263.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B5" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>244.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>203.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B7" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B8" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>182</v>
+      </c>
+      <c r="D8" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B10" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B11" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B14" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>29</v>
+      </c>
+      <c r="C15" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B16" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>127</v>
+      </c>
+      <c r="D16" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B18" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>120</v>
+      </c>
+      <c r="D18" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>84</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B21" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B24" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>142</v>
+      </c>
+      <c r="D25" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B26" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>157.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B27" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>173.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B29" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B30" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>21</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B33" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>134.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B34" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>141</v>
+      </c>
+      <c r="D34" t="n">
+        <v>165</v>
+      </c>
+      <c r="E34" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B35" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>83</v>
+      </c>
+      <c r="G36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B37" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>90</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B38" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>